--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdSpotexInvestTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdSpotexInvestTrade001.xlsx
@@ -1,72 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11880" windowHeight="5985"/>
+    <workbookView xWindow="240" yWindow="135" windowWidth="14805" windowHeight="7980"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
+    <t>有效状态</t>
+  </si>
+  <si>
+    <t>业务编号</t>
+  </si>
+  <si>
+    <t>委托代码</t>
+  </si>
+  <si>
     <t>组合代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组合名称</t>
+  </si>
+  <si>
+    <t>交易类型</t>
+  </si>
+  <si>
+    <t>货币对</t>
   </si>
   <si>
     <t>交易方向</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>业务编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有效状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>组合名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>交易日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>货币对</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>清算速度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>交割日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>即期汇率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>交易货币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>交易货币金额</t>
@@ -75,56 +61,41 @@
     <t>对应货币</t>
   </si>
   <si>
+    <t>对应货币金额</t>
+  </si>
+  <si>
     <t>折美元金额</t>
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>对应货币金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>委托代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="#,##0.00_);\(#,##0.00\)"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -137,48 +108,26 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -188,39 +137,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -299,142 +248,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -442,84 +415,66 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="24.875" customWidth="1"/>
-    <col min="2" max="3" width="27.875" customWidth="1"/>
-    <col min="4" max="4" width="26.375" customWidth="1"/>
-    <col min="5" max="5" width="26.875" customWidth="1"/>
-    <col min="6" max="6" width="28.25" customWidth="1"/>
-    <col min="7" max="7" width="29.75" customWidth="1"/>
-    <col min="8" max="8" width="31.875" customWidth="1"/>
-    <col min="9" max="9" width="18.875" customWidth="1"/>
-    <col min="10" max="10" width="35.25" customWidth="1"/>
-    <col min="11" max="11" width="35.375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="33.375" style="5" customWidth="1"/>
-    <col min="13" max="13" width="16.875" customWidth="1"/>
-    <col min="14" max="14" width="57.25" style="5" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
-    <col min="16" max="16" width="23.75" style="5" customWidth="1"/>
-    <col min="17" max="17" width="13.5" style="5" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
         <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>